--- a/output/ValueSet-BRTerminologiaSuspeitaDiagnostica.xlsx
+++ b/output/ValueSet-BRTerminologiaSuspeitaDiagnostica.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="102">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Suspeita Diagnóstica (ValueSet)</t>
+    <t>Suspeita Diagnóstica</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-16T14:11:40.0457007+00:00</t>
+    <t>2026-10-01T14:11:40.0457007+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,10 +99,217 @@
     <t>BooleanType[false]</t>
   </si>
   <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>B342</t>
+  </si>
+  <si>
+    <t>Infecção por coronavírus de localização não especificada</t>
+  </si>
+  <si>
+    <t>B04</t>
+  </si>
+  <si>
+    <t>Varíola dos macacos [Monkeypox]</t>
+  </si>
+  <si>
+    <t>A90</t>
+  </si>
+  <si>
+    <t>Dengue [dengue clássico]</t>
+  </si>
+  <si>
+    <t>A928</t>
+  </si>
+  <si>
+    <t>Outras febres virais especificadas transmitidas por mosquitos</t>
+  </si>
+  <si>
+    <t>A938</t>
+  </si>
+  <si>
+    <t>Outras febres virais especificadas transmitidas por artrópodes</t>
+  </si>
+  <si>
+    <t>A920</t>
+  </si>
+  <si>
+    <t>Febre de Chikungunya</t>
+  </si>
+  <si>
+    <t>A95</t>
+  </si>
+  <si>
+    <t>Febre amarela</t>
+  </si>
+  <si>
+    <t>A950</t>
+  </si>
+  <si>
+    <t>Febre amarela silvestre</t>
+  </si>
+  <si>
+    <t>A951</t>
+  </si>
+  <si>
+    <t>Febre amarela urbana</t>
+  </si>
+  <si>
+    <t>A959</t>
+  </si>
+  <si>
+    <t>Febre amarela não especificada</t>
+  </si>
+  <si>
+    <t>A930</t>
+  </si>
+  <si>
+    <t>Febre de oropouche</t>
+  </si>
+  <si>
+    <t>A923</t>
+  </si>
+  <si>
+    <t>Infecção pelo vírus West Nile</t>
+  </si>
+  <si>
+    <t>J10</t>
+  </si>
+  <si>
+    <t>Influenza devida a outro vírus da influenza [gripe] identificado</t>
+  </si>
+  <si>
+    <t>J11</t>
+  </si>
+  <si>
+    <t>Influenza (gripe) devida a vírus não identificado</t>
+  </si>
+  <si>
+    <t>B974</t>
+  </si>
+  <si>
+    <t>Vírus sincicial respiratório, como causa de doenças classificadas em outros capítulos</t>
+  </si>
+  <si>
+    <t>B05</t>
+  </si>
+  <si>
+    <t>Sarampo</t>
+  </si>
+  <si>
+    <t>B059</t>
+  </si>
+  <si>
+    <t>Sarampo sem complicação</t>
+  </si>
+  <si>
+    <t>B06</t>
+  </si>
+  <si>
+    <t>Rubéola</t>
+  </si>
+  <si>
+    <t>P350</t>
+  </si>
+  <si>
+    <t>Síndrome da rubéola congênita</t>
+  </si>
+  <si>
+    <t>B01</t>
+  </si>
+  <si>
+    <t>Varicela</t>
+  </si>
+  <si>
+    <t>B03</t>
+  </si>
+  <si>
+    <t>Varíola</t>
+  </si>
+  <si>
+    <t>A37</t>
+  </si>
+  <si>
+    <t>Coqueluche</t>
+  </si>
+  <si>
+    <t>A379</t>
+  </si>
+  <si>
+    <t>Coqueluche não especificada</t>
+  </si>
+  <si>
+    <t>A36</t>
+  </si>
+  <si>
+    <t>Difteria</t>
+  </si>
+  <si>
+    <t>A369</t>
+  </si>
+  <si>
+    <t>Difteria não especificada</t>
+  </si>
+  <si>
+    <t>A00</t>
+  </si>
+  <si>
+    <t>Cólera</t>
+  </si>
+  <si>
+    <t>A009</t>
+  </si>
+  <si>
+    <t>Cólera não especificada</t>
+  </si>
+  <si>
+    <t>B24</t>
+  </si>
+  <si>
+    <t>Doença pelo vírus da imunodeficiência humana [HIV] não especificada</t>
+  </si>
+  <si>
+    <t>B20</t>
+  </si>
+  <si>
+    <t>Doença pelo HIV resultando em doenças infecciosas e parasitárias</t>
+  </si>
+  <si>
+    <t>Z114</t>
+  </si>
+  <si>
+    <t>Exame especial de rastreamento de vírus da imunodeficiência humana [HIV]</t>
+  </si>
+  <si>
+    <t>B19</t>
+  </si>
+  <si>
+    <t>Hepatite viral não especificada</t>
+  </si>
+  <si>
+    <t>B15</t>
+  </si>
+  <si>
+    <t>Hepatite aguda A</t>
+  </si>
+  <si>
+    <t>B16</t>
+  </si>
+  <si>
+    <t>Hepatite aguda B</t>
+  </si>
+  <si>
+    <t>B171</t>
+  </si>
+  <si>
+    <t>Hepatite aguda C</t>
+  </si>
+  <si>
+    <t>B172</t>
+  </si>
+  <si>
+    <t>Hepatite aguda E</t>
   </si>
   <si>
     <t/>
@@ -375,7 +582,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -386,26 +593,312 @@
       <c r="A1" t="s" s="1">
         <v>28</v>
       </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
